--- a/ploy/resources/sample/PoolResultLib.xlsx
+++ b/ploy/resources/sample/PoolResultLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="PoolResultLib" sheetId="1" r:id="rId1"/>
@@ -32,32 +32,6 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-下注下限&amp;下注上限，模式ID，第X个倍数档位-修改后权重值|……；模式ID，第X个倍数档位-修改后权重值|……#下注下限&amp;下注上限，模式ID，第X个倍数档位-修改后权重值|……；模式ID，第X个倍数档位-修改后权重值|……
-1&amp;500000_1,3-0|4-0|5-0#500000&amp;999999999_1,0-0|1-0|2-0;2,4-0|5-0;3,6-0#
-下注金额在1~500000内时，常规模式（1）中5-10倍、10-15倍、15-20倍中奖权重改为0
-下注金额在500000~999999999时，常规模式（1）中0-1倍、1-2倍、2-5倍中奖权重改为0；樱桃模式（2）中10-15倍、15-20倍中奖权重改为0；明星模式中（3）中20-50倍中奖权重改为0
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="F1" authorId="0">
       <text>
         <r>
@@ -137,12 +111,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="E12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+风险增量万分比</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="35">
   <si>
     <t>id</t>
   </si>
@@ -223,6 +219,30 @@
   </si>
   <si>
     <t>吸水池-3</t>
+  </si>
+  <si>
+    <t>空袭</t>
+  </si>
+  <si>
+    <t>30_1</t>
+  </si>
+  <si>
+    <t>40_1</t>
+  </si>
+  <si>
+    <t>50_1</t>
+  </si>
+  <si>
+    <t>60_1</t>
+  </si>
+  <si>
+    <t>150_1</t>
+  </si>
+  <si>
+    <t>250_1</t>
+  </si>
+  <si>
+    <t>400_1</t>
   </si>
 </sst>
 </file>
@@ -394,12 +414,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -883,19 +903,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1218,7 +1238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
@@ -1321,16 +1341,16 @@
       <c r="D5" s="7">
         <v>1</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>8000</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>999999</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1347,16 +1367,16 @@
       <c r="D6" s="7">
         <v>2</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <v>6000</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <v>8000</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1373,16 +1393,16 @@
       <c r="D7" s="7">
         <v>3</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <v>4000</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <v>6000</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="9" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1399,16 +1419,16 @@
       <c r="D8" s="7">
         <v>4</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <v>2000</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>4000</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1425,16 +1445,16 @@
       <c r="D9" s="7">
         <v>5</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <v>0</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <v>2000</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1451,16 +1471,16 @@
       <c r="D10" s="7">
         <v>6</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
         <v>-1000</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <v>0</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="9" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1477,16 +1497,198 @@
       <c r="D11" s="7">
         <v>7</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
         <v>-999999</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <v>-1000</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:8">
+      <c r="A12" s="6">
+        <v>2008</v>
+      </c>
+      <c r="B12" s="6">
+        <v>400400</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="10">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="8">
+        <v>8000</v>
+      </c>
+      <c r="G12" s="8">
+        <v>999999</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:8">
+      <c r="A13" s="6">
+        <v>2009</v>
+      </c>
+      <c r="B13" s="6">
+        <v>400400</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="10">
+        <v>2</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="8">
+        <v>6000</v>
+      </c>
+      <c r="G13" s="8">
+        <v>8000</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:8">
+      <c r="A14" s="6">
+        <v>2010</v>
+      </c>
+      <c r="B14" s="6">
+        <v>400400</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="10">
+        <v>3</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="8">
+        <v>4000</v>
+      </c>
+      <c r="G14" s="8">
+        <v>6000</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:8">
+      <c r="A15" s="6">
+        <v>2011</v>
+      </c>
+      <c r="B15" s="6">
+        <v>400400</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="10">
+        <v>4</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="8">
+        <v>2000</v>
+      </c>
+      <c r="G15" s="8">
+        <v>4000</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:8">
+      <c r="A16" s="6">
+        <v>2012</v>
+      </c>
+      <c r="B16" s="6">
+        <v>400400</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="10">
+        <v>5</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0</v>
+      </c>
+      <c r="G16" s="8">
+        <v>2000</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:8">
+      <c r="A17" s="6">
+        <v>2013</v>
+      </c>
+      <c r="B17" s="6">
+        <v>400400</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="10">
+        <v>6</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="8">
+        <v>-1000</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:8">
+      <c r="A18" s="6">
+        <v>2014</v>
+      </c>
+      <c r="B18" s="6">
+        <v>400400</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="10">
+        <v>7</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="8">
+        <v>-999999</v>
+      </c>
+      <c r="G18" s="8">
+        <v>-1000</v>
+      </c>
+      <c r="H18" s="9" t="s">
         <v>26</v>
       </c>
     </row>
